--- a/Data/collapsed database manual cases/puebla_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/puebla_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E508CE7-08EC-C543-8DA9-272692067624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAA3824-61C7-3D45-B831-5134D9EE10D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14287" uniqueCount="3003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14289" uniqueCount="3004">
   <si>
     <t>uniqueid</t>
   </si>
@@ -9045,6 +9045,9 @@
   </si>
   <si>
     <t>PCPP</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/p/DQUTiV5kzzG/</t>
   </si>
 </sst>
 </file>
@@ -71189,7 +71192,7 @@
         <v>3001</v>
       </c>
     </row>
-    <row r="1457" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1457">
         <v>21199</v>
       </c>
@@ -71201,6 +71204,12 @@
       </c>
       <c r="F1457" t="s">
         <v>3000</v>
+      </c>
+      <c r="H1457" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1457" t="s">
+        <v>3003</v>
       </c>
     </row>
   </sheetData>
